--- a/_workspace/huni-dbmap/04_review/discount-mapping-review.xlsx
+++ b/_workspace/huni-dbmap/04_review/discount-mapping-review.xlsx
@@ -701,7 +701,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
